--- a/examples/example_config.xlsx
+++ b/examples/example_config.xlsx
@@ -7,9 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="简单配置" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="高级配置" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="温度扫描" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="配置" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -415,8 +413,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -426,382 +430,378 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>CPU</t>
+          <t>name</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>GPU</t>
+          <t>attribute</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Ambient</t>
+          <t>value</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>idle</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>5</v>
-      </c>
-      <c r="C2" t="n">
-        <v>2</v>
+          <t>case1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>powerDissipation</t>
+        </is>
       </c>
       <c r="D2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>15</v>
-      </c>
-      <c r="C3" t="n">
-        <v>10</v>
+          <t>case1</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>GPU</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>powerDissipation</t>
+        </is>
       </c>
       <c r="D3" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>heavy</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>30</v>
-      </c>
-      <c r="C4" t="n">
-        <v>20</v>
+          <t>case1</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>DDR</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>powerDissipation</t>
+        </is>
       </c>
       <c r="D4" t="n">
-        <v>35</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>stress</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>50</v>
-      </c>
-      <c r="C5" t="n">
-        <v>35</v>
-      </c>
-      <c r="D5" t="n">
-        <v>45</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>config_name</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>CPU</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>GPU</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Heatsink.Material.density</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Heatsink.Material.specificHeat</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>CPU.Size@width</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>CPU.Size@depth</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Ambient</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>aluminum_small</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>15</v>
-      </c>
-      <c r="C2" t="n">
-        <v>10</v>
-      </c>
-      <c r="D2" t="n">
-        <v>2700</v>
-      </c>
-      <c r="E2" t="n">
-        <v>900</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="H2" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>aluminum_large</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>20</v>
-      </c>
-      <c r="C3" t="n">
-        <v>15</v>
-      </c>
-      <c r="D3" t="n">
-        <v>2700</v>
-      </c>
-      <c r="E3" t="n">
-        <v>900</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="H3" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>copper_small</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>15</v>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>8900</v>
-      </c>
-      <c r="E4" t="n">
-        <v>385</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="H4" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>copper_large</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>25</v>
-      </c>
-      <c r="C5" t="n">
-        <v>18</v>
+          <t>case1</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Heatsink</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Material.density</t>
+        </is>
       </c>
       <c r="D5" t="n">
         <v>8900</v>
       </c>
-      <c r="E5" t="n">
-        <v>385</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="H5" t="n">
-        <v>35</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>config_name</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>CPU</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>GPU</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Ambient</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>temp_0C</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>20</v>
-      </c>
-      <c r="C2" t="n">
-        <v>10</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>temp_15C</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>20</v>
-      </c>
-      <c r="C3" t="n">
-        <v>10</v>
-      </c>
-      <c r="D3" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>temp_25C</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>20</v>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>temp_35C</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>20</v>
-      </c>
-      <c r="C5" t="n">
-        <v>10</v>
-      </c>
-      <c r="D5" t="n">
-        <v>35</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>temp_45C</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>20</v>
-      </c>
-      <c r="C6" t="n">
-        <v>10</v>
+          <t>case1</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Heatsink</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Material.conductivity</t>
+        </is>
       </c>
       <c r="D6" t="n">
-        <v>45</v>
+        <v>400</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>temp_55C</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
+          <t>case1</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>temperature</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>case2</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>powerDissipation</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>case2</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>GPU</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>powerDissipation</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>case2</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>DDR</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>powerDissipation</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>case2</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Heatsink</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Material.density</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>8500</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>case2</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Heatsink</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Material.conductivity</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>case2</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>temperature</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>case3</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>powerDissipation</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
         <v>20</v>
       </c>
-      <c r="C7" t="n">
-        <v>10</v>
-      </c>
-      <c r="D7" t="n">
-        <v>55</v>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>case3</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>GPU</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>powerDissipation</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>case3</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>DDR</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>powerDissipation</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>case3</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Heatsink</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Material.density</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>2700</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>case3</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Heatsink</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Material.conductivity</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>case3</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>temperature</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
